--- a/sources/BANQUE_OFFICIELLE_NOVAFRATE_V2_CARTE_RESIDENT.xlsx
+++ b/sources/BANQUE_OFFICIELLE_NOVAFRATE_V2_CARTE_RESIDENT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Chatbot_civique2\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112F97BB-04AA-4325-B38E-EDD14344FEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C3203-DC93-409F-9C0B-804E5648C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Banque_CR" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Standard_V2" sheetId="3" r:id="rId3"/>
     <sheet name="Sources_Fichiers" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5365,9 +5365,6 @@
   </si>
   <si>
     <t>6 ans.</t>
-  </si>
-  <si>
-    <t>À 3 ans.</t>
   </si>
   <si>
     <t>16 ans.</t>
@@ -6858,6 +6855,9 @@
   </si>
   <si>
     <t>Retenez : Les élèves handicapés ont le droit d'être avec les autres élèves = école inclusive</t>
+  </si>
+  <si>
+    <t>3 ans.</t>
   </si>
 </sst>
 </file>
@@ -7669,7 +7669,7 @@
         <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>34</v>
@@ -7740,7 +7740,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -7811,7 +7811,7 @@
         <v>61</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>62</v>
@@ -7882,7 +7882,7 @@
         <v>73</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>62</v>
@@ -7953,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>62</v>
@@ -8024,7 +8024,7 @@
         <v>94</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>62</v>
@@ -8080,13 +8080,13 @@
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>2140</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>2141</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>2142</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>83</v>
@@ -8095,7 +8095,7 @@
         <v>101</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>62</v>
@@ -8166,7 +8166,7 @@
         <v>111</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>62</v>
@@ -8237,7 +8237,7 @@
         <v>121</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>62</v>
@@ -8290,7 +8290,7 @@
         <v>125</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>127</v>
@@ -8308,7 +8308,7 @@
         <v>130</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>62</v>
@@ -8361,7 +8361,7 @@
         <v>135</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>136</v>
@@ -8370,7 +8370,7 @@
         <v>137</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>32</v>
@@ -8379,7 +8379,7 @@
         <v>138</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>62</v>
@@ -8574,7 +8574,7 @@
         <v>164</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>165</v>
@@ -8716,13 +8716,13 @@
         <v>183</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>184</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>185</v>
@@ -8734,7 +8734,7 @@
         <v>186</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>178</v>
@@ -8787,7 +8787,7 @@
         <v>190</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>191</v>
@@ -8805,7 +8805,7 @@
         <v>194</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>178</v>
@@ -8876,7 +8876,7 @@
         <v>204</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>178</v>
@@ -8935,10 +8935,10 @@
         <v>211</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>83</v>
@@ -8947,7 +8947,7 @@
         <v>212</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>178</v>
@@ -9018,7 +9018,7 @@
         <v>220</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>178</v>
@@ -9089,7 +9089,7 @@
         <v>228</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>178</v>
@@ -9151,7 +9151,7 @@
         <v>235</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>83</v>
@@ -9160,7 +9160,7 @@
         <v>236</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>178</v>
@@ -9231,7 +9231,7 @@
         <v>246</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>34</v>
@@ -9281,10 +9281,10 @@
         <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>251</v>
@@ -9293,7 +9293,7 @@
         <v>252</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>83</v>
@@ -9302,7 +9302,7 @@
         <v>253</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>178</v>
@@ -9355,7 +9355,7 @@
         <v>256</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>129</v>
@@ -9373,7 +9373,7 @@
         <v>259</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>178</v>
@@ -9429,13 +9429,13 @@
         <v>265</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>266</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>32</v>
@@ -9444,7 +9444,7 @@
         <v>267</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>178</v>
@@ -9515,7 +9515,7 @@
         <v>277</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>62</v>
@@ -9571,13 +9571,13 @@
         <v>126</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>2150</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>2149</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>2151</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>83</v>
@@ -9586,7 +9586,7 @@
         <v>283</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>34</v>
@@ -9657,7 +9657,7 @@
         <v>292</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>34</v>
@@ -9728,7 +9728,7 @@
         <v>301</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>62</v>
@@ -9799,7 +9799,7 @@
         <v>311</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>62</v>
@@ -9870,7 +9870,7 @@
         <v>321</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>62</v>
@@ -9941,7 +9941,7 @@
         <v>331</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>62</v>
@@ -10003,7 +10003,7 @@
         <v>337</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>83</v>
@@ -10012,7 +10012,7 @@
         <v>338</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>62</v>
@@ -10083,7 +10083,7 @@
         <v>347</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>62</v>
@@ -10136,13 +10136,13 @@
         <v>351</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>126</v>
@@ -10154,7 +10154,7 @@
         <v>352</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>62</v>
@@ -10225,7 +10225,7 @@
         <v>359</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>178</v>
@@ -10296,7 +10296,7 @@
         <v>369</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>178</v>
@@ -10367,7 +10367,7 @@
         <v>379</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>62</v>
@@ -10438,7 +10438,7 @@
         <v>391</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>178</v>
@@ -10509,7 +10509,7 @@
         <v>402</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>62</v>
@@ -10518,7 +10518,7 @@
         <v>403</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>404</v>
@@ -10562,10 +10562,10 @@
         <v>407</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>408</v>
@@ -10580,7 +10580,7 @@
         <v>410</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>62</v>
@@ -10651,7 +10651,7 @@
         <v>421</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>178</v>
@@ -10713,7 +10713,7 @@
         <v>429</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>72</v>
@@ -10722,7 +10722,7 @@
         <v>430</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>178</v>
@@ -10775,16 +10775,16 @@
         <v>436</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>2202</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>2205</v>
-      </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>2203</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>2204</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>83</v>
@@ -10793,7 +10793,7 @@
         <v>437</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>178</v>
@@ -10846,16 +10846,16 @@
         <v>442</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>129</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>32</v>
@@ -10864,7 +10864,7 @@
         <v>443</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>178</v>
@@ -10920,13 +10920,13 @@
         <v>129</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>1941</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>1942</v>
-      </c>
       <c r="J48" s="2" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>83</v>
@@ -10935,7 +10935,7 @@
         <v>449</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>178</v>
@@ -10944,7 +10944,7 @@
         <v>450</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>451</v>
@@ -10985,13 +10985,13 @@
         <v>406</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>454</v>
@@ -11003,10 +11003,10 @@
         <v>83</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>178</v>
@@ -11015,7 +11015,7 @@
         <v>456</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>457</v>
@@ -11062,7 +11062,7 @@
         <v>460</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>461</v>
@@ -11074,10 +11074,10 @@
         <v>72</v>
       </c>
       <c r="L50" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>2183</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>2184</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>178</v>
@@ -11086,10 +11086,10 @@
         <v>463</v>
       </c>
       <c r="P50" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="Q50" s="2" t="s">
         <v>2185</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>2186</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>38</v>
@@ -11148,7 +11148,7 @@
         <v>470</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>178</v>
@@ -11219,7 +11219,7 @@
         <v>480</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>178</v>
@@ -11278,7 +11278,7 @@
         <v>487</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>488</v>
@@ -11290,7 +11290,7 @@
         <v>489</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>178</v>
@@ -11343,13 +11343,13 @@
         <v>493</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>495</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>496</v>
@@ -11361,7 +11361,7 @@
         <v>497</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>62</v>
@@ -11411,7 +11411,7 @@
         <v>406</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>502</v>
@@ -11429,22 +11429,22 @@
         <v>32</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O55" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="P55" s="2" t="s">
         <v>2160</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="Q55" s="2" t="s">
         <v>2161</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>2162</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>38</v>
@@ -11485,7 +11485,7 @@
         <v>507</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>508</v>
@@ -11494,16 +11494,16 @@
         <v>398</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>62</v>
@@ -11515,7 +11515,7 @@
         <v>510</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>38</v>
@@ -11574,7 +11574,7 @@
         <v>517</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>178</v>
@@ -11645,7 +11645,7 @@
         <v>527</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>34</v>
@@ -11716,7 +11716,7 @@
         <v>536</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>62</v>
@@ -11769,16 +11769,16 @@
         <v>541</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>542</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>32</v>
@@ -11787,7 +11787,7 @@
         <v>543</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>62</v>
@@ -11840,7 +11840,7 @@
         <v>548</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>549</v>
@@ -11849,7 +11849,7 @@
         <v>550</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>60</v>
@@ -11858,7 +11858,7 @@
         <v>551</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>34</v>
@@ -11867,7 +11867,7 @@
         <v>552</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>491</v>
@@ -11911,7 +11911,7 @@
         <v>554</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>555</v>
@@ -11920,7 +11920,7 @@
         <v>556</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>72</v>
@@ -11929,7 +11929,7 @@
         <v>557</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>62</v>
@@ -12000,7 +12000,7 @@
         <v>567</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>62</v>
@@ -12071,7 +12071,7 @@
         <v>575</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>62</v>
@@ -12142,7 +12142,7 @@
         <v>585</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>34</v>
@@ -12195,13 +12195,13 @@
         <v>590</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="H66" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I66" s="2" t="s">
         <v>2209</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>2210</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>591</v>
@@ -12213,7 +12213,7 @@
         <v>592</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>178</v>
@@ -12222,7 +12222,7 @@
         <v>518</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>593</v>
@@ -12266,7 +12266,7 @@
         <v>595</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>596</v>
@@ -12284,7 +12284,7 @@
         <v>599</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>178</v>
@@ -12355,7 +12355,7 @@
         <v>609</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>178</v>
@@ -12364,10 +12364,10 @@
         <v>610</v>
       </c>
       <c r="P68" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="Q68" s="2" t="s">
         <v>2193</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>2194</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>38</v>
@@ -12411,7 +12411,7 @@
         <v>605</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>613</v>
@@ -12423,10 +12423,10 @@
         <v>72</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>178</v>
@@ -12435,7 +12435,7 @@
         <v>615</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>457</v>
@@ -12476,13 +12476,13 @@
         <v>406</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>617</v>
@@ -12494,10 +12494,10 @@
         <v>83</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>178</v>
@@ -12506,10 +12506,10 @@
         <v>619</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>38</v>
@@ -12568,7 +12568,7 @@
         <v>625</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>178</v>
@@ -12630,7 +12630,7 @@
         <v>631</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>72</v>
@@ -12639,7 +12639,7 @@
         <v>632</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>178</v>
@@ -12710,7 +12710,7 @@
         <v>641</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>178</v>
@@ -12766,7 +12766,7 @@
         <v>502</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>647</v>
@@ -12781,7 +12781,7 @@
         <v>649</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>178</v>
@@ -12852,7 +12852,7 @@
         <v>657</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>178</v>
@@ -12905,16 +12905,16 @@
         <v>662</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>516</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>32</v>
@@ -12923,7 +12923,7 @@
         <v>664</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>62</v>
@@ -12994,7 +12994,7 @@
         <v>672</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>62</v>
@@ -13065,7 +13065,7 @@
         <v>682</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>178</v>
@@ -13124,7 +13124,7 @@
         <v>137</v>
       </c>
       <c r="I79" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>689</v>
@@ -13136,7 +13136,7 @@
         <v>690</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>178</v>
@@ -13192,10 +13192,10 @@
         <v>696</v>
       </c>
       <c r="H80" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="I80" s="2" t="s">
         <v>1979</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>1980</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>697</v>
@@ -13207,7 +13207,7 @@
         <v>698</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>178</v>
@@ -13260,16 +13260,16 @@
         <v>702</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>1982</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="I81" s="2" t="s">
         <v>1983</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="J81" s="2" t="s">
         <v>1984</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>1985</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>83</v>
@@ -13278,7 +13278,7 @@
         <v>703</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>178</v>
@@ -13349,7 +13349,7 @@
         <v>712</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>178</v>
@@ -13420,7 +13420,7 @@
         <v>719</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>62</v>
@@ -13491,7 +13491,7 @@
         <v>727</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>178</v>
@@ -13562,7 +13562,7 @@
         <v>735</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>178</v>
@@ -13633,7 +13633,7 @@
         <v>744</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>178</v>
@@ -13704,7 +13704,7 @@
         <v>754</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>178</v>
@@ -13775,7 +13775,7 @@
         <v>764</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>178</v>
@@ -13846,7 +13846,7 @@
         <v>770</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>178</v>
@@ -13905,7 +13905,7 @@
         <v>776</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>777</v>
@@ -13917,7 +13917,7 @@
         <v>778</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>178</v>
@@ -13970,7 +13970,7 @@
         <v>785</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>786</v>
@@ -13988,7 +13988,7 @@
         <v>789</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>62</v>
@@ -14044,7 +14044,7 @@
         <v>796</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>797</v>
@@ -14059,7 +14059,7 @@
         <v>799</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>178</v>
@@ -14130,7 +14130,7 @@
         <v>810</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>62</v>
@@ -14186,13 +14186,13 @@
         <v>126</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>816</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>83</v>
@@ -14201,7 +14201,7 @@
         <v>817</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>62</v>
@@ -14257,7 +14257,7 @@
         <v>823</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>824</v>
@@ -14272,7 +14272,7 @@
         <v>826</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>62</v>
@@ -14343,7 +14343,7 @@
         <v>836</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>178</v>
@@ -14402,7 +14402,7 @@
         <v>842</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>126</v>
@@ -14414,7 +14414,7 @@
         <v>843</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>34</v>
@@ -14485,7 +14485,7 @@
         <v>853</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>178</v>
@@ -14556,7 +14556,7 @@
         <v>863</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>34</v>
@@ -14627,7 +14627,7 @@
         <v>872</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>178</v>
@@ -14698,7 +14698,7 @@
         <v>882</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>34</v>
@@ -14837,10 +14837,10 @@
         <v>60</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>178</v>
@@ -14911,7 +14911,7 @@
         <v>912</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>178</v>
@@ -14982,7 +14982,7 @@
         <v>918</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>178</v>
@@ -15053,7 +15053,7 @@
         <v>928</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>62</v>
@@ -15124,7 +15124,7 @@
         <v>938</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>178</v>
@@ -15180,13 +15180,13 @@
         <v>941</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>942</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>32</v>
@@ -15195,7 +15195,7 @@
         <v>943</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>178</v>
@@ -15266,7 +15266,7 @@
         <v>951</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="N109" s="2" t="s">
         <v>34</v>
@@ -15337,7 +15337,7 @@
         <v>961</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="N110" s="2" t="s">
         <v>62</v>
@@ -15408,7 +15408,7 @@
         <v>971</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="N111" s="2" t="s">
         <v>178</v>
@@ -15470,7 +15470,7 @@
         <v>979</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>83</v>
@@ -15479,7 +15479,7 @@
         <v>980</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>62</v>
@@ -15550,7 +15550,7 @@
         <v>989</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>178</v>
@@ -15621,7 +15621,7 @@
         <v>999</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>178</v>
@@ -15692,7 +15692,7 @@
         <v>1009</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>62</v>
@@ -15748,7 +15748,7 @@
         <v>1015</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>1016</v>
@@ -15763,7 +15763,7 @@
         <v>1018</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>62</v>
@@ -15819,7 +15819,7 @@
         <v>1022</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>1023</v>
@@ -15834,7 +15834,7 @@
         <v>1025</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>62</v>
@@ -15905,7 +15905,7 @@
         <v>1035</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>62</v>
@@ -15976,7 +15976,7 @@
         <v>1044</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>62</v>
@@ -16035,7 +16035,7 @@
         <v>1051</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>1052</v>
@@ -16047,7 +16047,7 @@
         <v>1053</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>62</v>
@@ -16118,7 +16118,7 @@
         <v>1063</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>178</v>
@@ -16171,7 +16171,7 @@
         <v>1068</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>1069</v>
@@ -16189,7 +16189,7 @@
         <v>1072</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>62</v>
@@ -16242,7 +16242,7 @@
         <v>1077</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>1078</v>
@@ -16251,7 +16251,7 @@
         <v>1079</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>83</v>
@@ -16260,7 +16260,7 @@
         <v>1080</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>62</v>
@@ -16331,7 +16331,7 @@
         <v>1089</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>62</v>
@@ -16402,7 +16402,7 @@
         <v>1099</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>62</v>
@@ -16473,7 +16473,7 @@
         <v>1107</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="N126" s="2" t="s">
         <v>62</v>
@@ -16544,7 +16544,7 @@
         <v>1115</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="N127" s="2" t="s">
         <v>62</v>
@@ -16615,7 +16615,7 @@
         <v>1125</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="N128" s="2" t="s">
         <v>62</v>
@@ -16674,10 +16674,10 @@
         <v>1134</v>
       </c>
       <c r="I129" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="J129" s="2" t="s">
         <v>2040</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>2041</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>83</v>
@@ -16686,7 +16686,7 @@
         <v>1135</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>62</v>
@@ -16757,7 +16757,7 @@
         <v>1146</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="N130" s="2" t="s">
         <v>178</v>
@@ -16828,7 +16828,7 @@
         <v>1155</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="N131" s="2" t="s">
         <v>62</v>
@@ -16899,7 +16899,7 @@
         <v>1163</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="N132" s="2" t="s">
         <v>62</v>
@@ -16952,16 +16952,16 @@
         <v>1168</v>
       </c>
       <c r="G133" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>2046</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="I133" s="2" t="s">
         <v>2047</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="J133" s="2" t="s">
         <v>2048</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>2049</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>83</v>
@@ -16970,7 +16970,7 @@
         <v>1171</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="N133" s="2" t="s">
         <v>62</v>
@@ -17041,7 +17041,7 @@
         <v>1181</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="N134" s="2" t="s">
         <v>62</v>
@@ -17094,16 +17094,16 @@
         <v>1186</v>
       </c>
       <c r="G135" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>2051</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="I135" s="2" t="s">
         <v>2052</v>
       </c>
-      <c r="I135" s="2" t="s">
+      <c r="J135" s="2" t="s">
         <v>2053</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>2054</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>83</v>
@@ -17112,7 +17112,7 @@
         <v>1188</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="N135" s="2" t="s">
         <v>62</v>
@@ -17165,7 +17165,7 @@
         <v>1193</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>276</v>
@@ -17183,7 +17183,7 @@
         <v>1195</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="N136" s="2" t="s">
         <v>62</v>
@@ -17192,7 +17192,7 @@
         <v>1196</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q136" s="2" t="s">
         <v>1197</v>
@@ -17239,7 +17239,7 @@
         <v>1200</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>1201</v>
@@ -17251,10 +17251,10 @@
         <v>32</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="N137" s="2" t="s">
         <v>62</v>
@@ -17322,10 +17322,10 @@
         <v>32</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>178</v>
@@ -17396,7 +17396,7 @@
         <v>1220</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="N139" s="2" t="s">
         <v>62</v>
@@ -17452,7 +17452,7 @@
         <v>1226</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>1162</v>
@@ -17467,7 +17467,7 @@
         <v>1228</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="N140" s="2" t="s">
         <v>178</v>
@@ -17529,7 +17529,7 @@
         <v>1236</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>32</v>
@@ -17538,7 +17538,7 @@
         <v>1237</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="N141" s="2" t="s">
         <v>62</v>
@@ -17609,7 +17609,7 @@
         <v>1246</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>62</v>
@@ -17662,7 +17662,7 @@
         <v>1251</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>1252</v>
@@ -17680,7 +17680,7 @@
         <v>1255</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="N143" s="2" t="s">
         <v>62</v>
@@ -17730,7 +17730,7 @@
         <v>1131</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>717</v>
@@ -17751,7 +17751,7 @@
         <v>1259</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="N144" s="2" t="s">
         <v>62</v>
@@ -17822,7 +17822,7 @@
         <v>1266</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="N145" s="2" t="s">
         <v>62</v>
@@ -17884,7 +17884,7 @@
         <v>1274</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>72</v>
@@ -17893,7 +17893,7 @@
         <v>1275</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="N146" s="2" t="s">
         <v>178</v>
@@ -17964,7 +17964,7 @@
         <v>1285</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="N147" s="2" t="s">
         <v>62</v>
@@ -18017,16 +18017,16 @@
         <v>1290</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>1291</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>32</v>
@@ -18035,7 +18035,7 @@
         <v>1292</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="N148" s="2" t="s">
         <v>178</v>
@@ -18091,7 +18091,7 @@
         <v>1326</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>1298</v>
@@ -18106,7 +18106,7 @@
         <v>1300</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>178</v>
@@ -18248,7 +18248,7 @@
         <v>1319</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>62</v>
@@ -18319,7 +18319,7 @@
         <v>1329</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="N152" s="2" t="s">
         <v>62</v>
@@ -18390,7 +18390,7 @@
         <v>1338</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>62</v>
@@ -18461,7 +18461,7 @@
         <v>1347</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>62</v>
@@ -18532,7 +18532,7 @@
         <v>1357</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>62</v>
@@ -18588,13 +18588,13 @@
         <v>1363</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>72</v>
@@ -18603,7 +18603,7 @@
         <v>1364</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="N156" s="2" t="s">
         <v>62</v>
@@ -18674,7 +18674,7 @@
         <v>1374</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>62</v>
@@ -18745,7 +18745,7 @@
         <v>1383</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>62</v>
@@ -18798,7 +18798,7 @@
         <v>1388</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>1389</v>
@@ -18816,7 +18816,7 @@
         <v>1392</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="N159" s="2" t="s">
         <v>62</v>
@@ -18943,7 +18943,7 @@
         <v>753</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="I161" s="2" t="s">
         <v>1409</v>
@@ -18958,7 +18958,7 @@
         <v>1411</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="N161" s="2" t="s">
         <v>62</v>
@@ -19017,7 +19017,7 @@
         <v>1417</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>1418</v>
@@ -19029,7 +19029,7 @@
         <v>1419</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>62</v>
@@ -19100,7 +19100,7 @@
         <v>1429</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="N163" s="2" t="s">
         <v>62</v>
@@ -19171,7 +19171,7 @@
         <v>1439</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>178</v>
@@ -19242,7 +19242,7 @@
         <v>1448</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="N165" s="2" t="s">
         <v>62</v>
@@ -19313,7 +19313,7 @@
         <v>1458</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="N166" s="2" t="s">
         <v>62</v>
@@ -19366,7 +19366,7 @@
         <v>1462</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>1463</v>
@@ -19384,7 +19384,7 @@
         <v>1466</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="N167" s="2" t="s">
         <v>62</v>
@@ -19508,7 +19508,7 @@
         <v>1481</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>1482</v>
@@ -19526,7 +19526,7 @@
         <v>1485</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>62</v>
@@ -19588,7 +19588,7 @@
         <v>1493</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="K170" s="2" t="s">
         <v>60</v>
@@ -19597,7 +19597,7 @@
         <v>1494</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="N170" s="2" t="s">
         <v>62</v>
@@ -19668,7 +19668,7 @@
         <v>1502</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="N171" s="2" t="s">
         <v>62</v>
@@ -19739,7 +19739,7 @@
         <v>1509</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="N172" s="2" t="s">
         <v>178</v>
@@ -19881,7 +19881,7 @@
         <v>1531</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>62</v>
@@ -19940,10 +19940,10 @@
         <v>1540</v>
       </c>
       <c r="I175" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J175" s="2" t="s">
         <v>2104</v>
-      </c>
-      <c r="J175" s="2" t="s">
-        <v>2105</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>72</v>
@@ -19952,7 +19952,7 @@
         <v>1541</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="N175" s="2" t="s">
         <v>62</v>
@@ -20023,7 +20023,7 @@
         <v>1551</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="N176" s="2" t="s">
         <v>62</v>
@@ -20085,7 +20085,7 @@
         <v>1559</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="K177" s="2" t="s">
         <v>32</v>
@@ -20094,7 +20094,7 @@
         <v>1560</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="N177" s="2" t="s">
         <v>178</v>
@@ -20156,7 +20156,7 @@
         <v>1568</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="K178" s="2" t="s">
         <v>72</v>
@@ -20165,7 +20165,7 @@
         <v>1569</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="N178" s="2" t="s">
         <v>178</v>
@@ -20218,7 +20218,7 @@
         <v>1574</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>1575</v>
@@ -20236,7 +20236,7 @@
         <v>1578</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>178</v>
@@ -20307,7 +20307,7 @@
         <v>1589</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N180" s="2" t="s">
         <v>178</v>
@@ -20378,7 +20378,7 @@
         <v>1599</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>178</v>
@@ -20434,13 +20434,13 @@
         <v>1604</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>663</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>72</v>
@@ -20449,7 +20449,7 @@
         <v>1605</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>178</v>
@@ -20520,7 +20520,7 @@
         <v>1616</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="N183" s="2" t="s">
         <v>178</v>
@@ -20591,7 +20591,7 @@
         <v>1626</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="N184" s="2" t="s">
         <v>62</v>
@@ -20662,7 +20662,7 @@
         <v>1636</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>178</v>
@@ -20733,7 +20733,7 @@
         <v>1646</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="N186" s="2" t="s">
         <v>62</v>
@@ -20804,7 +20804,7 @@
         <v>1653</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>178</v>
@@ -20875,7 +20875,7 @@
         <v>1663</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="N188" s="2" t="s">
         <v>62</v>
@@ -20946,7 +20946,7 @@
         <v>1673</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="N189" s="2" t="s">
         <v>62</v>
@@ -21017,7 +21017,7 @@
         <v>1683</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="N190" s="2" t="s">
         <v>62</v>
@@ -21088,7 +21088,7 @@
         <v>1692</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="N191" s="2" t="s">
         <v>62</v>
@@ -21159,7 +21159,7 @@
         <v>1702</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="N192" s="2" t="s">
         <v>62</v>
@@ -21230,7 +21230,7 @@
         <v>1712</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="N193" s="2" t="s">
         <v>62</v>
@@ -21301,7 +21301,7 @@
         <v>1722</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="N194" s="2" t="s">
         <v>62</v>
@@ -21372,7 +21372,7 @@
         <v>1732</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>62</v>
@@ -21443,7 +21443,7 @@
         <v>1742</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="N196" s="2" t="s">
         <v>62</v>
@@ -21493,7 +21493,7 @@
         <v>1537</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>1747</v>
@@ -21514,7 +21514,7 @@
         <v>1751</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="N197" s="2" t="s">
         <v>62</v>
@@ -21585,7 +21585,7 @@
         <v>1761</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="N198" s="2" t="s">
         <v>62</v>
@@ -21644,31 +21644,31 @@
         <v>1768</v>
       </c>
       <c r="I199" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J199" s="2" t="s">
         <v>1769</v>
-      </c>
-      <c r="J199" s="2" t="s">
-        <v>1770</v>
       </c>
       <c r="K199" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="N199" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O199" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="P199" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="P199" s="2" t="s">
+      <c r="Q199" s="2" t="s">
         <v>1773</v>
-      </c>
-      <c r="Q199" s="2" t="s">
-        <v>1774</v>
       </c>
       <c r="R199" s="2" t="s">
         <v>38</v>
@@ -21691,7 +21691,7 @@
     </row>
     <row r="200" spans="1:23" ht="41.4">
       <c r="A200" s="2" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>24</v>
@@ -21706,40 +21706,40 @@
         <v>1525</v>
       </c>
       <c r="F200" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G200" s="2" t="s">
         <v>1776</v>
       </c>
-      <c r="G200" s="2" t="s">
+      <c r="H200" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="I200" s="2" t="s">
         <v>1777</v>
       </c>
-      <c r="H200" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="I200" s="2" t="s">
+      <c r="J200" s="2" t="s">
         <v>1778</v>
-      </c>
-      <c r="J200" s="2" t="s">
-        <v>1779</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="N200" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O200" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="P200" s="2" t="s">
         <v>1781</v>
       </c>
-      <c r="P200" s="2" t="s">
+      <c r="Q200" s="2" t="s">
         <v>1782</v>
-      </c>
-      <c r="Q200" s="2" t="s">
-        <v>1783</v>
       </c>
       <c r="R200" s="2" t="s">
         <v>38</v>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="201" spans="1:23" ht="55.2">
       <c r="A201" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>24</v>
@@ -21777,40 +21777,40 @@
         <v>1537</v>
       </c>
       <c r="F201" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G201" s="2" t="s">
         <v>1785</v>
       </c>
-      <c r="G201" s="2" t="s">
+      <c r="H201" s="2" t="s">
         <v>1786</v>
       </c>
-      <c r="H201" s="2" t="s">
+      <c r="I201" s="2" t="s">
         <v>1787</v>
       </c>
-      <c r="I201" s="2" t="s">
+      <c r="J201" s="2" t="s">
         <v>1788</v>
-      </c>
-      <c r="J201" s="2" t="s">
-        <v>1789</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="N201" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O201" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="P201" s="2" t="s">
         <v>1791</v>
       </c>
-      <c r="P201" s="2" t="s">
+      <c r="Q201" s="2" t="s">
         <v>1792</v>
-      </c>
-      <c r="Q201" s="2" t="s">
-        <v>1793</v>
       </c>
       <c r="R201" s="2" t="s">
         <v>38</v>
@@ -21833,7 +21833,7 @@
     </row>
     <row r="202" spans="1:23" ht="41.4">
       <c r="A202" s="2" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>24</v>
@@ -21848,40 +21848,40 @@
         <v>1537</v>
       </c>
       <c r="F202" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G202" s="2" t="s">
         <v>1795</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="H202" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I202" s="2" t="s">
         <v>1796</v>
       </c>
-      <c r="H202" s="2" t="s">
-        <v>2135</v>
-      </c>
-      <c r="I202" s="2" t="s">
+      <c r="J202" s="2" t="s">
         <v>1797</v>
-      </c>
-      <c r="J202" s="2" t="s">
-        <v>1798</v>
       </c>
       <c r="K202" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="M202" s="2" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="N202" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O202" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="P202" s="2" t="s">
         <v>1800</v>
       </c>
-      <c r="P202" s="2" t="s">
+      <c r="Q202" s="2" t="s">
         <v>1801</v>
-      </c>
-      <c r="Q202" s="2" t="s">
-        <v>1802</v>
       </c>
       <c r="R202" s="2" t="s">
         <v>38</v>
@@ -21904,7 +21904,7 @@
     </row>
     <row r="203" spans="1:23" ht="55.2">
       <c r="A203" s="2" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>24</v>
@@ -21919,40 +21919,40 @@
         <v>1525</v>
       </c>
       <c r="F203" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G203" s="2" t="s">
         <v>1804</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="H203" s="2" t="s">
         <v>1805</v>
       </c>
-      <c r="H203" s="2" t="s">
+      <c r="I203" s="2" t="s">
         <v>1806</v>
       </c>
-      <c r="I203" s="2" t="s">
+      <c r="J203" s="2" t="s">
         <v>1807</v>
-      </c>
-      <c r="J203" s="2" t="s">
-        <v>1808</v>
       </c>
       <c r="K203" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="M203" s="2" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="N203" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O203" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="P203" s="2" t="s">
         <v>1810</v>
       </c>
-      <c r="P203" s="2" t="s">
+      <c r="Q203" s="2" t="s">
         <v>1811</v>
-      </c>
-      <c r="Q203" s="2" t="s">
-        <v>1812</v>
       </c>
       <c r="R203" s="2" t="s">
         <v>38</v>
@@ -21975,7 +21975,7 @@
     </row>
     <row r="204" spans="1:23" ht="41.4">
       <c r="A204" s="2" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>24</v>
@@ -21990,40 +21990,40 @@
         <v>1525</v>
       </c>
       <c r="F204" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H204" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="I204" s="2" t="s">
         <v>2137</v>
       </c>
-      <c r="H204" s="2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="I204" s="2" t="s">
-        <v>2138</v>
-      </c>
       <c r="J204" s="2" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="K204" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L204" s="2" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="N204" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O204" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="P204" s="2" t="s">
         <v>1817</v>
       </c>
-      <c r="P204" s="2" t="s">
+      <c r="Q204" s="2" t="s">
         <v>1818</v>
-      </c>
-      <c r="Q204" s="2" t="s">
-        <v>1819</v>
       </c>
       <c r="R204" s="2" t="s">
         <v>38</v>
@@ -22046,7 +22046,7 @@
     </row>
     <row r="205" spans="1:23" ht="55.2">
       <c r="A205" s="2" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>24</v>
@@ -22061,40 +22061,40 @@
         <v>1537</v>
       </c>
       <c r="F205" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G205" s="2" t="s">
         <v>1821</v>
       </c>
-      <c r="G205" s="2" t="s">
+      <c r="H205" s="2" t="s">
         <v>1822</v>
       </c>
-      <c r="H205" s="2" t="s">
+      <c r="I205" s="2" t="s">
         <v>1823</v>
       </c>
-      <c r="I205" s="2" t="s">
+      <c r="J205" s="2" t="s">
         <v>1824</v>
-      </c>
-      <c r="J205" s="2" t="s">
-        <v>1825</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="M205" s="2" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="N205" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O205" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="P205" s="2" t="s">
         <v>1827</v>
       </c>
-      <c r="P205" s="2" t="s">
+      <c r="Q205" s="2" t="s">
         <v>1828</v>
-      </c>
-      <c r="Q205" s="2" t="s">
-        <v>1829</v>
       </c>
       <c r="R205" s="2" t="s">
         <v>38</v>
@@ -22174,7 +22174,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22186,31 +22186,31 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>1832</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1833</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B4">
         <f>COUNTA(Banque_CR!A2:A1000)</f>
         <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -22222,14 +22222,14 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B5">
         <f>COUNTIF(Banque_CR!C2:C1000,1)</f>
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E5" t="s">
         <v>72</v>
@@ -22241,14 +22241,14 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B6">
         <f>COUNTIF(Banque_CR!C2:C1000,2)</f>
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -22260,14 +22260,14 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B7">
         <f>COUNTIF(Banque_CR!C2:C1000,3)</f>
         <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
@@ -22279,17 +22279,17 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B8">
         <f>COUNTIF(Banque_CR!C2:C1000,4)</f>
         <v>45</v>
       </c>
       <c r="C8" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E8" t="s">
         <v>1844</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1845</v>
       </c>
       <c r="F8">
         <f>SUM(F4:F7)</f>
@@ -22298,31 +22298,31 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B9">
         <f>COUNTIF(Banque_CR!C2:C1000,5)</f>
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B10">
         <f>COUNTIF(Banque_CR!U2:U1000,"À vérifier")</f>
         <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -22332,10 +22332,10 @@
     </row>
     <row r="14" spans="1:8" ht="27.6">
       <c r="A14" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1851</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1852</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -22344,10 +22344,10 @@
     </row>
     <row r="15" spans="1:8" ht="55.2">
       <c r="A15" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1853</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1854</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -22356,10 +22356,10 @@
     </row>
     <row r="16" spans="1:8" ht="41.4">
       <c r="A16" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>1855</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1856</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -22368,10 +22368,10 @@
     </row>
     <row r="17" spans="1:6" ht="41.4">
       <c r="A17" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>1857</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1858</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -22380,10 +22380,10 @@
     </row>
     <row r="18" spans="1:6" ht="41.4">
       <c r="A18" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>1859</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1860</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -22413,7 +22413,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22421,16 +22421,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1862</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>1863</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>1864</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -22441,10 +22441,10 @@
         <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1866</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -22455,24 +22455,24 @@
         <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1869</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1870</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -22483,10 +22483,10 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1871</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -22497,10 +22497,10 @@
         <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1873</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -22511,7 +22511,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -22525,10 +22525,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1876</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -22539,10 +22539,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1878</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -22553,21 +22553,21 @@
         <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1880</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1882</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1883</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -22581,10 +22581,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1884</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1885</v>
       </c>
     </row>
   </sheetData>
@@ -22605,7 +22605,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22616,13 +22616,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>1887</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>1888</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -22636,7 +22636,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -22650,7 +22650,7 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -22664,7 +22664,7 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -22678,7 +22678,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -22692,7 +22692,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
   </sheetData>

--- a/sources/BANQUE_OFFICIELLE_NOVAFRATE_V2_CARTE_RESIDENT.xlsx
+++ b/sources/BANQUE_OFFICIELLE_NOVAFRATE_V2_CARTE_RESIDENT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Chatbot_civique2\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C3203-DC93-409F-9C0B-804E5648C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112F97BB-04AA-4325-B38E-EDD14344FEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Banque_CR" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Standard_V2" sheetId="3" r:id="rId3"/>
     <sheet name="Sources_Fichiers" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5365,6 +5365,9 @@
   </si>
   <si>
     <t>6 ans.</t>
+  </si>
+  <si>
+    <t>À 3 ans.</t>
   </si>
   <si>
     <t>16 ans.</t>
@@ -6855,9 +6858,6 @@
   </si>
   <si>
     <t>Retenez : Les élèves handicapés ont le droit d'être avec les autres élèves = école inclusive</t>
-  </si>
-  <si>
-    <t>3 ans.</t>
   </si>
 </sst>
 </file>
@@ -7669,7 +7669,7 @@
         <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>34</v>
@@ -7740,7 +7740,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -7811,7 +7811,7 @@
         <v>61</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>62</v>
@@ -7882,7 +7882,7 @@
         <v>73</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>62</v>
@@ -7953,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>62</v>
@@ -8024,7 +8024,7 @@
         <v>94</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>62</v>
@@ -8080,13 +8080,13 @@
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>83</v>
@@ -8095,7 +8095,7 @@
         <v>101</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>62</v>
@@ -8166,7 +8166,7 @@
         <v>111</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>62</v>
@@ -8237,7 +8237,7 @@
         <v>121</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>62</v>
@@ -8290,7 +8290,7 @@
         <v>125</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>127</v>
@@ -8308,7 +8308,7 @@
         <v>130</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>62</v>
@@ -8361,7 +8361,7 @@
         <v>135</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>136</v>
@@ -8370,7 +8370,7 @@
         <v>137</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>32</v>
@@ -8379,7 +8379,7 @@
         <v>138</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>62</v>
@@ -8574,7 +8574,7 @@
         <v>164</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>165</v>
@@ -8716,13 +8716,13 @@
         <v>183</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>184</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>185</v>
@@ -8734,7 +8734,7 @@
         <v>186</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>178</v>
@@ -8787,7 +8787,7 @@
         <v>190</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>191</v>
@@ -8805,7 +8805,7 @@
         <v>194</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>178</v>
@@ -8876,7 +8876,7 @@
         <v>204</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>178</v>
@@ -8935,10 +8935,10 @@
         <v>211</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>83</v>
@@ -8947,7 +8947,7 @@
         <v>212</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>178</v>
@@ -9018,7 +9018,7 @@
         <v>220</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>178</v>
@@ -9089,7 +9089,7 @@
         <v>228</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>178</v>
@@ -9151,7 +9151,7 @@
         <v>235</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>83</v>
@@ -9160,7 +9160,7 @@
         <v>236</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>178</v>
@@ -9231,7 +9231,7 @@
         <v>246</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>34</v>
@@ -9281,10 +9281,10 @@
         <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>251</v>
@@ -9293,7 +9293,7 @@
         <v>252</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>83</v>
@@ -9302,7 +9302,7 @@
         <v>253</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>178</v>
@@ -9355,7 +9355,7 @@
         <v>256</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>129</v>
@@ -9373,7 +9373,7 @@
         <v>259</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>178</v>
@@ -9429,13 +9429,13 @@
         <v>265</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>266</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>32</v>
@@ -9444,7 +9444,7 @@
         <v>267</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>178</v>
@@ -9515,7 +9515,7 @@
         <v>277</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>62</v>
@@ -9571,13 +9571,13 @@
         <v>126</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>2149</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>2148</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>83</v>
@@ -9586,7 +9586,7 @@
         <v>283</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>34</v>
@@ -9657,7 +9657,7 @@
         <v>292</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>34</v>
@@ -9728,7 +9728,7 @@
         <v>301</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>62</v>
@@ -9799,7 +9799,7 @@
         <v>311</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>62</v>
@@ -9870,7 +9870,7 @@
         <v>321</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>62</v>
@@ -9941,7 +9941,7 @@
         <v>331</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>62</v>
@@ -10003,7 +10003,7 @@
         <v>337</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>83</v>
@@ -10012,7 +10012,7 @@
         <v>338</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>62</v>
@@ -10083,7 +10083,7 @@
         <v>347</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>62</v>
@@ -10136,13 +10136,13 @@
         <v>351</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>1928</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>2151</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>1927</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>126</v>
@@ -10154,7 +10154,7 @@
         <v>352</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>62</v>
@@ -10225,7 +10225,7 @@
         <v>359</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>178</v>
@@ -10296,7 +10296,7 @@
         <v>369</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>178</v>
@@ -10367,7 +10367,7 @@
         <v>379</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>62</v>
@@ -10438,7 +10438,7 @@
         <v>391</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>178</v>
@@ -10509,7 +10509,7 @@
         <v>402</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>62</v>
@@ -10518,7 +10518,7 @@
         <v>403</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>404</v>
@@ -10562,10 +10562,10 @@
         <v>407</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>408</v>
@@ -10580,7 +10580,7 @@
         <v>410</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>62</v>
@@ -10651,7 +10651,7 @@
         <v>421</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>178</v>
@@ -10713,7 +10713,7 @@
         <v>429</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>72</v>
@@ -10722,7 +10722,7 @@
         <v>430</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>178</v>
@@ -10775,16 +10775,16 @@
         <v>436</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>2204</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>2203</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>83</v>
@@ -10793,7 +10793,7 @@
         <v>437</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>178</v>
@@ -10846,16 +10846,16 @@
         <v>442</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>129</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>32</v>
@@ -10864,7 +10864,7 @@
         <v>443</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>178</v>
@@ -10920,13 +10920,13 @@
         <v>129</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>83</v>
@@ -10935,7 +10935,7 @@
         <v>449</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>178</v>
@@ -10944,7 +10944,7 @@
         <v>450</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>451</v>
@@ -10985,13 +10985,13 @@
         <v>406</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>454</v>
@@ -11003,10 +11003,10 @@
         <v>83</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>178</v>
@@ -11015,7 +11015,7 @@
         <v>456</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>457</v>
@@ -11062,7 +11062,7 @@
         <v>460</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>461</v>
@@ -11074,10 +11074,10 @@
         <v>72</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>178</v>
@@ -11086,10 +11086,10 @@
         <v>463</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>38</v>
@@ -11148,7 +11148,7 @@
         <v>470</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>178</v>
@@ -11219,7 +11219,7 @@
         <v>480</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>178</v>
@@ -11278,7 +11278,7 @@
         <v>487</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>488</v>
@@ -11290,7 +11290,7 @@
         <v>489</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>178</v>
@@ -11343,13 +11343,13 @@
         <v>493</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>495</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>496</v>
@@ -11361,7 +11361,7 @@
         <v>497</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>62</v>
@@ -11411,7 +11411,7 @@
         <v>406</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>502</v>
@@ -11429,22 +11429,22 @@
         <v>32</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>38</v>
@@ -11485,7 +11485,7 @@
         <v>507</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>508</v>
@@ -11494,16 +11494,16 @@
         <v>398</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>62</v>
@@ -11515,7 +11515,7 @@
         <v>510</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>38</v>
@@ -11574,7 +11574,7 @@
         <v>517</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>178</v>
@@ -11645,7 +11645,7 @@
         <v>527</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>34</v>
@@ -11716,7 +11716,7 @@
         <v>536</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>62</v>
@@ -11769,16 +11769,16 @@
         <v>541</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>542</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>32</v>
@@ -11787,7 +11787,7 @@
         <v>543</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>62</v>
@@ -11840,7 +11840,7 @@
         <v>548</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>549</v>
@@ -11849,7 +11849,7 @@
         <v>550</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>60</v>
@@ -11858,7 +11858,7 @@
         <v>551</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>34</v>
@@ -11867,7 +11867,7 @@
         <v>552</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>491</v>
@@ -11911,7 +11911,7 @@
         <v>554</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>555</v>
@@ -11920,7 +11920,7 @@
         <v>556</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>72</v>
@@ -11929,7 +11929,7 @@
         <v>557</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>62</v>
@@ -12000,7 +12000,7 @@
         <v>567</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>62</v>
@@ -12071,7 +12071,7 @@
         <v>575</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>62</v>
@@ -12142,7 +12142,7 @@
         <v>585</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>34</v>
@@ -12195,13 +12195,13 @@
         <v>590</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>591</v>
@@ -12213,7 +12213,7 @@
         <v>592</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>178</v>
@@ -12222,7 +12222,7 @@
         <v>518</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>593</v>
@@ -12266,7 +12266,7 @@
         <v>595</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>596</v>
@@ -12284,7 +12284,7 @@
         <v>599</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>178</v>
@@ -12355,7 +12355,7 @@
         <v>609</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>178</v>
@@ -12364,10 +12364,10 @@
         <v>610</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>38</v>
@@ -12411,7 +12411,7 @@
         <v>605</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>613</v>
@@ -12423,10 +12423,10 @@
         <v>72</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>178</v>
@@ -12435,7 +12435,7 @@
         <v>615</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>457</v>
@@ -12476,13 +12476,13 @@
         <v>406</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>617</v>
@@ -12494,10 +12494,10 @@
         <v>83</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>178</v>
@@ -12506,10 +12506,10 @@
         <v>619</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>38</v>
@@ -12568,7 +12568,7 @@
         <v>625</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>178</v>
@@ -12630,7 +12630,7 @@
         <v>631</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>72</v>
@@ -12639,7 +12639,7 @@
         <v>632</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>178</v>
@@ -12710,7 +12710,7 @@
         <v>641</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>178</v>
@@ -12766,7 +12766,7 @@
         <v>502</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>647</v>
@@ -12781,7 +12781,7 @@
         <v>649</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>178</v>
@@ -12852,7 +12852,7 @@
         <v>657</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>178</v>
@@ -12905,16 +12905,16 @@
         <v>662</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>516</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>32</v>
@@ -12923,7 +12923,7 @@
         <v>664</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>62</v>
@@ -12994,7 +12994,7 @@
         <v>672</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>62</v>
@@ -13065,7 +13065,7 @@
         <v>682</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>178</v>
@@ -13124,7 +13124,7 @@
         <v>137</v>
       </c>
       <c r="I79" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>689</v>
@@ -13136,7 +13136,7 @@
         <v>690</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>178</v>
@@ -13192,10 +13192,10 @@
         <v>696</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>697</v>
@@ -13207,7 +13207,7 @@
         <v>698</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>178</v>
@@ -13260,16 +13260,16 @@
         <v>702</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>83</v>
@@ -13278,7 +13278,7 @@
         <v>703</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>178</v>
@@ -13349,7 +13349,7 @@
         <v>712</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>178</v>
@@ -13420,7 +13420,7 @@
         <v>719</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>62</v>
@@ -13491,7 +13491,7 @@
         <v>727</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>178</v>
@@ -13562,7 +13562,7 @@
         <v>735</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>178</v>
@@ -13633,7 +13633,7 @@
         <v>744</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>178</v>
@@ -13704,7 +13704,7 @@
         <v>754</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>178</v>
@@ -13775,7 +13775,7 @@
         <v>764</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>178</v>
@@ -13846,7 +13846,7 @@
         <v>770</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>178</v>
@@ -13905,7 +13905,7 @@
         <v>776</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>777</v>
@@ -13917,7 +13917,7 @@
         <v>778</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>178</v>
@@ -13970,7 +13970,7 @@
         <v>785</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>786</v>
@@ -13988,7 +13988,7 @@
         <v>789</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>62</v>
@@ -14044,7 +14044,7 @@
         <v>796</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>797</v>
@@ -14059,7 +14059,7 @@
         <v>799</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>178</v>
@@ -14130,7 +14130,7 @@
         <v>810</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>62</v>
@@ -14186,13 +14186,13 @@
         <v>126</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>816</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>83</v>
@@ -14201,7 +14201,7 @@
         <v>817</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>62</v>
@@ -14257,7 +14257,7 @@
         <v>823</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>824</v>
@@ -14272,7 +14272,7 @@
         <v>826</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>62</v>
@@ -14343,7 +14343,7 @@
         <v>836</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>178</v>
@@ -14402,7 +14402,7 @@
         <v>842</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>126</v>
@@ -14414,7 +14414,7 @@
         <v>843</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>34</v>
@@ -14485,7 +14485,7 @@
         <v>853</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>178</v>
@@ -14556,7 +14556,7 @@
         <v>863</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>34</v>
@@ -14627,7 +14627,7 @@
         <v>872</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>178</v>
@@ -14698,7 +14698,7 @@
         <v>882</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>34</v>
@@ -14837,10 +14837,10 @@
         <v>60</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>178</v>
@@ -14911,7 +14911,7 @@
         <v>912</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>178</v>
@@ -14982,7 +14982,7 @@
         <v>918</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>178</v>
@@ -15053,7 +15053,7 @@
         <v>928</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>62</v>
@@ -15124,7 +15124,7 @@
         <v>938</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>178</v>
@@ -15180,13 +15180,13 @@
         <v>941</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>942</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>32</v>
@@ -15195,7 +15195,7 @@
         <v>943</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>178</v>
@@ -15266,7 +15266,7 @@
         <v>951</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="N109" s="2" t="s">
         <v>34</v>
@@ -15337,7 +15337,7 @@
         <v>961</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="N110" s="2" t="s">
         <v>62</v>
@@ -15408,7 +15408,7 @@
         <v>971</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="N111" s="2" t="s">
         <v>178</v>
@@ -15470,7 +15470,7 @@
         <v>979</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>83</v>
@@ -15479,7 +15479,7 @@
         <v>980</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>62</v>
@@ -15550,7 +15550,7 @@
         <v>989</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>178</v>
@@ -15621,7 +15621,7 @@
         <v>999</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>178</v>
@@ -15692,7 +15692,7 @@
         <v>1009</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>62</v>
@@ -15748,7 +15748,7 @@
         <v>1015</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>1016</v>
@@ -15763,7 +15763,7 @@
         <v>1018</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>62</v>
@@ -15819,7 +15819,7 @@
         <v>1022</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>1023</v>
@@ -15834,7 +15834,7 @@
         <v>1025</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>62</v>
@@ -15905,7 +15905,7 @@
         <v>1035</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>62</v>
@@ -15976,7 +15976,7 @@
         <v>1044</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>62</v>
@@ -16035,7 +16035,7 @@
         <v>1051</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>1052</v>
@@ -16047,7 +16047,7 @@
         <v>1053</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>62</v>
@@ -16118,7 +16118,7 @@
         <v>1063</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>178</v>
@@ -16171,7 +16171,7 @@
         <v>1068</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>1069</v>
@@ -16189,7 +16189,7 @@
         <v>1072</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>62</v>
@@ -16242,7 +16242,7 @@
         <v>1077</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>1078</v>
@@ -16251,7 +16251,7 @@
         <v>1079</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>83</v>
@@ -16260,7 +16260,7 @@
         <v>1080</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>62</v>
@@ -16331,7 +16331,7 @@
         <v>1089</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>62</v>
@@ -16402,7 +16402,7 @@
         <v>1099</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>62</v>
@@ -16473,7 +16473,7 @@
         <v>1107</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="N126" s="2" t="s">
         <v>62</v>
@@ -16544,7 +16544,7 @@
         <v>1115</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="N127" s="2" t="s">
         <v>62</v>
@@ -16615,7 +16615,7 @@
         <v>1125</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="N128" s="2" t="s">
         <v>62</v>
@@ -16674,10 +16674,10 @@
         <v>1134</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>83</v>
@@ -16686,7 +16686,7 @@
         <v>1135</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>62</v>
@@ -16757,7 +16757,7 @@
         <v>1146</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="N130" s="2" t="s">
         <v>178</v>
@@ -16828,7 +16828,7 @@
         <v>1155</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="N131" s="2" t="s">
         <v>62</v>
@@ -16899,7 +16899,7 @@
         <v>1163</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="N132" s="2" t="s">
         <v>62</v>
@@ -16952,16 +16952,16 @@
         <v>1168</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>83</v>
@@ -16970,7 +16970,7 @@
         <v>1171</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="N133" s="2" t="s">
         <v>62</v>
@@ -17041,7 +17041,7 @@
         <v>1181</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="N134" s="2" t="s">
         <v>62</v>
@@ -17094,16 +17094,16 @@
         <v>1186</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>83</v>
@@ -17112,7 +17112,7 @@
         <v>1188</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="N135" s="2" t="s">
         <v>62</v>
@@ -17165,7 +17165,7 @@
         <v>1193</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>276</v>
@@ -17183,7 +17183,7 @@
         <v>1195</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="N136" s="2" t="s">
         <v>62</v>
@@ -17192,7 +17192,7 @@
         <v>1196</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="Q136" s="2" t="s">
         <v>1197</v>
@@ -17239,7 +17239,7 @@
         <v>1200</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>1201</v>
@@ -17251,10 +17251,10 @@
         <v>32</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="N137" s="2" t="s">
         <v>62</v>
@@ -17322,10 +17322,10 @@
         <v>32</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>178</v>
@@ -17396,7 +17396,7 @@
         <v>1220</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="N139" s="2" t="s">
         <v>62</v>
@@ -17452,7 +17452,7 @@
         <v>1226</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>1162</v>
@@ -17467,7 +17467,7 @@
         <v>1228</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="N140" s="2" t="s">
         <v>178</v>
@@ -17529,7 +17529,7 @@
         <v>1236</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>32</v>
@@ -17538,7 +17538,7 @@
         <v>1237</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="N141" s="2" t="s">
         <v>62</v>
@@ -17609,7 +17609,7 @@
         <v>1246</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>62</v>
@@ -17662,7 +17662,7 @@
         <v>1251</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>1252</v>
@@ -17680,7 +17680,7 @@
         <v>1255</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="N143" s="2" t="s">
         <v>62</v>
@@ -17730,7 +17730,7 @@
         <v>1131</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>717</v>
@@ -17751,7 +17751,7 @@
         <v>1259</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="N144" s="2" t="s">
         <v>62</v>
@@ -17822,7 +17822,7 @@
         <v>1266</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="N145" s="2" t="s">
         <v>62</v>
@@ -17884,7 +17884,7 @@
         <v>1274</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>72</v>
@@ -17893,7 +17893,7 @@
         <v>1275</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="N146" s="2" t="s">
         <v>178</v>
@@ -17964,7 +17964,7 @@
         <v>1285</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="N147" s="2" t="s">
         <v>62</v>
@@ -18017,16 +18017,16 @@
         <v>1290</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>1291</v>
       </c>
       <c r="I148" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="J148" s="2" t="s">
         <v>2071</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>2070</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>32</v>
@@ -18035,7 +18035,7 @@
         <v>1292</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="N148" s="2" t="s">
         <v>178</v>
@@ -18091,7 +18091,7 @@
         <v>1326</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>1298</v>
@@ -18106,7 +18106,7 @@
         <v>1300</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>178</v>
@@ -18248,7 +18248,7 @@
         <v>1319</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>62</v>
@@ -18319,7 +18319,7 @@
         <v>1329</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="N152" s="2" t="s">
         <v>62</v>
@@ -18390,7 +18390,7 @@
         <v>1338</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>62</v>
@@ -18461,7 +18461,7 @@
         <v>1347</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>62</v>
@@ -18532,7 +18532,7 @@
         <v>1357</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>62</v>
@@ -18588,13 +18588,13 @@
         <v>1363</v>
       </c>
       <c r="H156" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I156" s="2" t="s">
         <v>2081</v>
       </c>
-      <c r="I156" s="2" t="s">
+      <c r="J156" s="2" t="s">
         <v>2080</v>
-      </c>
-      <c r="J156" s="2" t="s">
-        <v>2079</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>72</v>
@@ -18603,7 +18603,7 @@
         <v>1364</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="N156" s="2" t="s">
         <v>62</v>
@@ -18674,7 +18674,7 @@
         <v>1374</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>62</v>
@@ -18745,7 +18745,7 @@
         <v>1383</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>62</v>
@@ -18798,7 +18798,7 @@
         <v>1388</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>1389</v>
@@ -18816,7 +18816,7 @@
         <v>1392</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="N159" s="2" t="s">
         <v>62</v>
@@ -18943,7 +18943,7 @@
         <v>753</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="I161" s="2" t="s">
         <v>1409</v>
@@ -18958,7 +18958,7 @@
         <v>1411</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="N161" s="2" t="s">
         <v>62</v>
@@ -19017,7 +19017,7 @@
         <v>1417</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>1418</v>
@@ -19029,7 +19029,7 @@
         <v>1419</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>62</v>
@@ -19100,7 +19100,7 @@
         <v>1429</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="N163" s="2" t="s">
         <v>62</v>
@@ -19171,7 +19171,7 @@
         <v>1439</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>178</v>
@@ -19242,7 +19242,7 @@
         <v>1448</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="N165" s="2" t="s">
         <v>62</v>
@@ -19313,7 +19313,7 @@
         <v>1458</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="N166" s="2" t="s">
         <v>62</v>
@@ -19366,7 +19366,7 @@
         <v>1462</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>1463</v>
@@ -19384,7 +19384,7 @@
         <v>1466</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="N167" s="2" t="s">
         <v>62</v>
@@ -19508,7 +19508,7 @@
         <v>1481</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>1482</v>
@@ -19526,7 +19526,7 @@
         <v>1485</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>62</v>
@@ -19588,7 +19588,7 @@
         <v>1493</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="K170" s="2" t="s">
         <v>60</v>
@@ -19597,7 +19597,7 @@
         <v>1494</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="N170" s="2" t="s">
         <v>62</v>
@@ -19668,7 +19668,7 @@
         <v>1502</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="N171" s="2" t="s">
         <v>62</v>
@@ -19739,7 +19739,7 @@
         <v>1509</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="N172" s="2" t="s">
         <v>178</v>
@@ -19881,7 +19881,7 @@
         <v>1531</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>62</v>
@@ -19940,10 +19940,10 @@
         <v>1540</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>72</v>
@@ -19952,7 +19952,7 @@
         <v>1541</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="N175" s="2" t="s">
         <v>62</v>
@@ -20023,7 +20023,7 @@
         <v>1551</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="N176" s="2" t="s">
         <v>62</v>
@@ -20085,7 +20085,7 @@
         <v>1559</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="K177" s="2" t="s">
         <v>32</v>
@@ -20094,7 +20094,7 @@
         <v>1560</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="N177" s="2" t="s">
         <v>178</v>
@@ -20156,7 +20156,7 @@
         <v>1568</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="K178" s="2" t="s">
         <v>72</v>
@@ -20165,7 +20165,7 @@
         <v>1569</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="N178" s="2" t="s">
         <v>178</v>
@@ -20218,7 +20218,7 @@
         <v>1574</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>1575</v>
@@ -20236,7 +20236,7 @@
         <v>1578</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>178</v>
@@ -20307,7 +20307,7 @@
         <v>1589</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="N180" s="2" t="s">
         <v>178</v>
@@ -20378,7 +20378,7 @@
         <v>1599</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>178</v>
@@ -20434,13 +20434,13 @@
         <v>1604</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>663</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>72</v>
@@ -20449,7 +20449,7 @@
         <v>1605</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>178</v>
@@ -20520,7 +20520,7 @@
         <v>1616</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="N183" s="2" t="s">
         <v>178</v>
@@ -20591,7 +20591,7 @@
         <v>1626</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="N184" s="2" t="s">
         <v>62</v>
@@ -20662,7 +20662,7 @@
         <v>1636</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>178</v>
@@ -20733,7 +20733,7 @@
         <v>1646</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="N186" s="2" t="s">
         <v>62</v>
@@ -20804,7 +20804,7 @@
         <v>1653</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>178</v>
@@ -20875,7 +20875,7 @@
         <v>1663</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="N188" s="2" t="s">
         <v>62</v>
@@ -20946,7 +20946,7 @@
         <v>1673</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="N189" s="2" t="s">
         <v>62</v>
@@ -21017,7 +21017,7 @@
         <v>1683</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="N190" s="2" t="s">
         <v>62</v>
@@ -21088,7 +21088,7 @@
         <v>1692</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="N191" s="2" t="s">
         <v>62</v>
@@ -21159,7 +21159,7 @@
         <v>1702</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="N192" s="2" t="s">
         <v>62</v>
@@ -21230,7 +21230,7 @@
         <v>1712</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="N193" s="2" t="s">
         <v>62</v>
@@ -21301,7 +21301,7 @@
         <v>1722</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="N194" s="2" t="s">
         <v>62</v>
@@ -21372,7 +21372,7 @@
         <v>1732</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>62</v>
@@ -21443,7 +21443,7 @@
         <v>1742</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="N196" s="2" t="s">
         <v>62</v>
@@ -21493,7 +21493,7 @@
         <v>1537</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>1747</v>
@@ -21514,7 +21514,7 @@
         <v>1751</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="N197" s="2" t="s">
         <v>62</v>
@@ -21585,7 +21585,7 @@
         <v>1761</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="N198" s="2" t="s">
         <v>62</v>
@@ -21644,31 +21644,31 @@
         <v>1768</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>2232</v>
+        <v>1769</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="K199" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="N199" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O199" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="P199" s="2" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="Q199" s="2" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="R199" s="2" t="s">
         <v>38</v>
@@ -21691,7 +21691,7 @@
     </row>
     <row r="200" spans="1:23" ht="41.4">
       <c r="A200" s="2" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>24</v>
@@ -21706,40 +21706,40 @@
         <v>1525</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="N200" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O200" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="R200" s="2" t="s">
         <v>38</v>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="201" spans="1:23" ht="55.2">
       <c r="A201" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>24</v>
@@ -21777,40 +21777,40 @@
         <v>1537</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="N201" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O201" s="2" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="P201" s="2" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="Q201" s="2" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="R201" s="2" t="s">
         <v>38</v>
@@ -21833,7 +21833,7 @@
     </row>
     <row r="202" spans="1:23" ht="41.4">
       <c r="A202" s="2" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>24</v>
@@ -21848,40 +21848,40 @@
         <v>1537</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="K202" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="M202" s="2" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="N202" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O202" s="2" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="P202" s="2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="Q202" s="2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="R202" s="2" t="s">
         <v>38</v>
@@ -21904,7 +21904,7 @@
     </row>
     <row r="203" spans="1:23" ht="55.2">
       <c r="A203" s="2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>24</v>
@@ -21919,40 +21919,40 @@
         <v>1525</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="K203" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="M203" s="2" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="N203" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O203" s="2" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="P203" s="2" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="Q203" s="2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="R203" s="2" t="s">
         <v>38</v>
@@ -21975,7 +21975,7 @@
     </row>
     <row r="204" spans="1:23" ht="41.4">
       <c r="A204" s="2" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>24</v>
@@ -21990,40 +21990,40 @@
         <v>1525</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="K204" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L204" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="N204" s="2" t="s">
         <v>178</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="P204" s="2" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="Q204" s="2" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="R204" s="2" t="s">
         <v>38</v>
@@ -22046,7 +22046,7 @@
     </row>
     <row r="205" spans="1:23" ht="55.2">
       <c r="A205" s="2" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>24</v>
@@ -22061,40 +22061,40 @@
         <v>1537</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="M205" s="2" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="N205" s="2" t="s">
         <v>62</v>
       </c>
       <c r="O205" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="P205" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="Q205" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="R205" s="2" t="s">
         <v>38</v>
@@ -22174,7 +22174,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22186,31 +22186,31 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B4">
         <f>COUNTA(Banque_CR!A2:A1000)</f>
         <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -22222,14 +22222,14 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B5">
         <f>COUNTIF(Banque_CR!C2:C1000,1)</f>
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="E5" t="s">
         <v>72</v>
@@ -22241,14 +22241,14 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B6">
         <f>COUNTIF(Banque_CR!C2:C1000,2)</f>
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -22260,14 +22260,14 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B7">
         <f>COUNTIF(Banque_CR!C2:C1000,3)</f>
         <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
@@ -22279,17 +22279,17 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B8">
         <f>COUNTIF(Banque_CR!C2:C1000,4)</f>
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="E8" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="F8">
         <f>SUM(F4:F7)</f>
@@ -22298,31 +22298,31 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B9">
         <f>COUNTIF(Banque_CR!C2:C1000,5)</f>
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B10">
         <f>COUNTIF(Banque_CR!U2:U1000,"À vérifier")</f>
         <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -22332,10 +22332,10 @@
     </row>
     <row r="14" spans="1:8" ht="27.6">
       <c r="A14" s="2" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -22344,10 +22344,10 @@
     </row>
     <row r="15" spans="1:8" ht="55.2">
       <c r="A15" s="2" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -22356,10 +22356,10 @@
     </row>
     <row r="16" spans="1:8" ht="41.4">
       <c r="A16" s="2" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -22368,10 +22368,10 @@
     </row>
     <row r="17" spans="1:6" ht="41.4">
       <c r="A17" s="2" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -22380,10 +22380,10 @@
     </row>
     <row r="18" spans="1:6" ht="41.4">
       <c r="A18" s="2" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -22413,7 +22413,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22421,16 +22421,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -22441,10 +22441,10 @@
         <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -22455,24 +22455,24 @@
         <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1867</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -22483,10 +22483,10 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -22497,10 +22497,10 @@
         <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -22511,7 +22511,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -22525,10 +22525,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -22539,10 +22539,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -22553,21 +22553,21 @@
         <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -22581,10 +22581,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
   </sheetData>
@@ -22605,7 +22605,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -22616,13 +22616,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -22636,7 +22636,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -22650,7 +22650,7 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -22664,7 +22664,7 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -22678,7 +22678,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -22692,7 +22692,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
   </sheetData>
